--- a/artfynd/A 46891-2019 artfynd.xlsx
+++ b/artfynd/A 46891-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46891-2019 artfynd.xlsx
+++ b/artfynd/A 46891-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,427 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114941810</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söder Hässleby  (Söder Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>513808</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6578708</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114941726</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söder Hässleby  (Söder Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>513828</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6578713</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114941669</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söder Hässleby (Söder Hässleby), Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>513776</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6578606</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114941925</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örebro (Örebro), Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>513816</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6578610</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46891-2019 artfynd.xlsx
+++ b/artfynd/A 46891-2019 artfynd.xlsx
@@ -3366,7 +3366,7 @@
         <v>118743289</v>
       </c>
       <c r="B26" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 46891-2019 artfynd.xlsx
+++ b/artfynd/A 46891-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3482,6 +3482,249 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120511448</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Söder Hässleby , Söder Hässleby , Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>513784</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6578686</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120510832</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Örebro, Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>513842</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6578665</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46891-2019 artfynd.xlsx
+++ b/artfynd/A 46891-2019 artfynd.xlsx
@@ -3484,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120511448</v>
+        <v>120510832</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,34 +3500,53 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söder Hässleby , Söder Hässleby , Nrk</t>
+          <t>Örebro, Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513784</v>
+        <v>513842</v>
       </c>
       <c r="R27" t="n">
-        <v>6578686</v>
+        <v>6578665</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3559,7 +3578,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3588,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120510832</v>
+        <v>120511448</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,53 +3631,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Örebro, Örebro, Nrk</t>
+          <t>Söder Hässleby , Söder Hässleby , Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513842</v>
+        <v>513784</v>
       </c>
       <c r="R28" t="n">
-        <v>6578665</v>
+        <v>6578686</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
